--- a/notes/coreMeasurement/coresScanned_Ai-Lun.xlsx
+++ b/notes/coreMeasurement/coresScanned_Ai-Lun.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temporal Ecology Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E9E1FE-83A5-4E9A-9C69-DA9CC39ED7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB32088-0F8A-40AD-A851-3AEC9FC47CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="1255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="1257">
   <si>
     <t>Stand</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4040,25 +4040,31 @@
     <t>Not in folder?</t>
   </si>
   <si>
-    <t>dark band of circles near 19, 28 doesn’t seem like crack so unmarked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rings from 25 to 32 slightly faint but visible </t>
-  </si>
-  <si>
-    <t>dark band of circles near rings 19, 28; doesn’t seem like crack so unmarked</t>
-  </si>
-  <si>
-    <t>crack marked before ring 4; check that it's not discoloration</t>
-  </si>
-  <si>
-    <t>ring 26 marked but not super visible</t>
-  </si>
-  <si>
-    <t>slightly faint ring between 172 and 174</t>
-  </si>
-  <si>
-    <t>dark band of circles before 72 unmarked, check that it's not a crack</t>
+    <t>Notes - DPI 6472</t>
+  </si>
+  <si>
+    <t>dark band of circles near rings 19, 28</t>
+  </si>
+  <si>
+    <t>dark band of circles before 72</t>
+  </si>
+  <si>
+    <t>dark bands of circles toward end (85, 86, 65)</t>
+  </si>
+  <si>
+    <t>discoloration near 55, 81, 82</t>
+  </si>
+  <si>
+    <t>dark ring of circles near 12</t>
+  </si>
+  <si>
+    <t>ring of circles near 70</t>
+  </si>
+  <si>
+    <t>ring 5 a bit faint but still visible</t>
+  </si>
+  <si>
+    <t>gap before 62, might affect ring placement</t>
   </si>
 </sst>
 </file>
@@ -13371,7 +13377,7 @@
     <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="60.109375" customWidth="1"/>
+    <col min="7" max="7" width="64.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -13394,7 +13400,7 @@
         <v>1244</v>
       </c>
       <c r="G1" t="s">
-        <v>220</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -13436,9 +13442,7 @@
       <c r="F3">
         <v>101</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>1251</v>
-      </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
@@ -13460,7 +13464,7 @@
         <v>103</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -13557,9 +13561,7 @@
       <c r="F9">
         <v>176</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>1248</v>
-      </c>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
@@ -13580,9 +13582,7 @@
       <c r="F10">
         <v>195</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>1252</v>
-      </c>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
@@ -13603,9 +13603,7 @@
       <c r="F11">
         <v>155</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>1249</v>
-      </c>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
@@ -13721,9 +13719,7 @@
       <c r="F17">
         <v>190</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>1253</v>
-      </c>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1">
       <c r="A18" s="2" t="s">
@@ -13760,7 +13756,7 @@
         <v>174</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13773,6 +13769,18 @@
       <c r="C20" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D20" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46155</v>
+      </c>
+      <c r="F20">
+        <v>87</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>1251</v>
+      </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
@@ -13784,6 +13792,15 @@
       <c r="C21" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D21" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E21" s="5">
+        <v>46155</v>
+      </c>
+      <c r="F21">
+        <v>243</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
@@ -13795,6 +13812,11 @@
       <c r="C22" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D22" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
@@ -13806,6 +13828,16 @@
       <c r="C23" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D23" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E23" s="5">
+        <v>46156</v>
+      </c>
+      <c r="F23">
+        <v>192</v>
+      </c>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
@@ -13817,6 +13849,15 @@
       <c r="C24" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D24" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E24" s="5">
+        <v>46156</v>
+      </c>
+      <c r="F24">
+        <v>59</v>
+      </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
@@ -13828,6 +13869,15 @@
       <c r="C25" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D25" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E25" s="5">
+        <v>46156</v>
+      </c>
+      <c r="F25">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
@@ -13839,6 +13889,18 @@
       <c r="C26" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D26" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E26" s="5">
+        <v>46156</v>
+      </c>
+      <c r="F26">
+        <v>68</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
@@ -13850,6 +13912,16 @@
       <c r="C27" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D27" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E27" s="5">
+        <v>46157</v>
+      </c>
+      <c r="F27">
+        <v>76</v>
+      </c>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
@@ -13861,6 +13933,15 @@
       <c r="C28" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D28" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E28" s="5">
+        <v>46157</v>
+      </c>
+      <c r="F28">
+        <v>269</v>
+      </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
@@ -13872,6 +13953,15 @@
       <c r="C29" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D29" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E29" s="5">
+        <v>46157</v>
+      </c>
+      <c r="F29">
+        <v>219</v>
+      </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
@@ -13883,6 +13973,18 @@
       <c r="C30" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D30" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E30" s="5">
+        <v>46162</v>
+      </c>
+      <c r="F30">
+        <v>143</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
@@ -13894,6 +13996,16 @@
       <c r="C31" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="D31" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E31" s="5">
+        <v>46162</v>
+      </c>
+      <c r="F31">
+        <v>113</v>
+      </c>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
@@ -13905,8 +14017,18 @@
       <c r="C32" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="D32" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E32" s="5">
+        <v>46162</v>
+      </c>
+      <c r="F32">
+        <v>135</v>
+      </c>
+      <c r="G32" s="8"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
         <v>704</v>
       </c>
@@ -13916,8 +14038,9 @@
       <c r="C33" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="G33" s="8"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
         <v>704</v>
       </c>
@@ -13927,8 +14050,18 @@
       <c r="C34" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="D34" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E34" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F34">
+        <v>81</v>
+      </c>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
         <v>704</v>
       </c>
@@ -13938,8 +14071,18 @@
       <c r="C35" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="D35" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E35" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F35">
+        <v>72</v>
+      </c>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
         <v>704</v>
       </c>
@@ -13949,8 +14092,18 @@
       <c r="C36" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="D36" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E36" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F36">
+        <v>83</v>
+      </c>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
         <v>704</v>
       </c>
@@ -13960,8 +14113,20 @@
       <c r="C37" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="D37" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E37" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F37">
+        <v>144</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
         <v>704</v>
       </c>
@@ -13971,8 +14136,18 @@
       <c r="C38" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="D38" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E38" s="5">
+        <v>46167</v>
+      </c>
+      <c r="F38">
+        <v>93</v>
+      </c>
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
         <v>704</v>
       </c>
@@ -13982,8 +14157,18 @@
       <c r="C39" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="D39" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E39" s="5">
+        <v>46167</v>
+      </c>
+      <c r="F39">
+        <v>56</v>
+      </c>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
         <v>704</v>
       </c>
@@ -13993,8 +14178,20 @@
       <c r="C40" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="D40" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E40" s="5">
+        <v>46167</v>
+      </c>
+      <c r="F40">
+        <v>164</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
         <v>704</v>
       </c>
@@ -14004,8 +14201,18 @@
       <c r="C41" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" s="2" customFormat="1">
+      <c r="D41" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E41" s="5">
+        <v>46167</v>
+      </c>
+      <c r="F41">
+        <v>236</v>
+      </c>
+      <c r="G41" s="8"/>
+    </row>
+    <row r="42" spans="1:7" s="2" customFormat="1">
       <c r="A42" s="2" t="s">
         <v>704</v>
       </c>
@@ -14017,7 +14224,7 @@
       </c>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1">
+    <row r="43" spans="1:7" s="2" customFormat="1">
       <c r="A43" s="2" t="s">
         <v>704</v>
       </c>
@@ -14029,7 +14236,7 @@
       </c>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" s="2" customFormat="1">
+    <row r="44" spans="1:7" s="2" customFormat="1">
       <c r="A44" s="2" t="s">
         <v>704</v>
       </c>
@@ -14041,7 +14248,7 @@
       </c>
       <c r="E44"/>
     </row>
-    <row r="45" spans="1:5" s="2" customFormat="1">
+    <row r="45" spans="1:7" s="2" customFormat="1">
       <c r="A45" s="2" t="s">
         <v>704</v>
       </c>
@@ -14053,7 +14260,7 @@
       </c>
       <c r="E45"/>
     </row>
-    <row r="46" spans="1:5" s="2" customFormat="1">
+    <row r="46" spans="1:7" s="2" customFormat="1">
       <c r="A46" s="2" t="s">
         <v>704</v>
       </c>
@@ -14065,7 +14272,7 @@
       </c>
       <c r="E46"/>
     </row>
-    <row r="47" spans="1:5" s="2" customFormat="1">
+    <row r="47" spans="1:7" s="2" customFormat="1">
       <c r="A47" s="2" t="s">
         <v>704</v>
       </c>
@@ -14077,7 +14284,7 @@
       </c>
       <c r="E47"/>
     </row>
-    <row r="48" spans="1:5" s="2" customFormat="1">
+    <row r="48" spans="1:7" s="2" customFormat="1">
       <c r="A48" s="2" t="s">
         <v>704</v>
       </c>
@@ -14198,6 +14405,15 @@
       <c r="C57" s="2" t="s">
         <v>413</v>
       </c>
+      <c r="D57" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E57" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F57">
+        <v>221</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
@@ -14209,6 +14425,7 @@
       <c r="C58" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
@@ -14231,6 +14448,15 @@
       <c r="C60" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="D60" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E60" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F60">
+        <v>385</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
@@ -14242,6 +14468,15 @@
       <c r="C61" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="D61" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E61" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F61">
+        <v>322</v>
+      </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
@@ -14253,6 +14488,15 @@
       <c r="C62" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="D62" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E62" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F62">
+        <v>295</v>
+      </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
@@ -14264,6 +14508,15 @@
       <c r="C63" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="D63" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E63" s="5">
+        <v>46178</v>
+      </c>
+      <c r="F63">
+        <v>170</v>
+      </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
@@ -14275,8 +14528,17 @@
       <c r="C64" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E64" s="5">
+        <v>46178</v>
+      </c>
+      <c r="F64">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="2" t="s">
         <v>704</v>
       </c>
@@ -14286,8 +14548,17 @@
       <c r="C65" s="2" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E65" s="5">
+        <v>46178</v>
+      </c>
+      <c r="F65">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="2" t="s">
         <v>704</v>
       </c>
@@ -14297,8 +14568,17 @@
       <c r="C66" s="2" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E66" s="5">
+        <v>46178</v>
+      </c>
+      <c r="F66">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="2" t="s">
         <v>704</v>
       </c>
@@ -14308,8 +14588,20 @@
       <c r="C67" s="2" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E67" s="5">
+        <v>46178</v>
+      </c>
+      <c r="F67">
+        <v>129</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
         <v>704</v>
       </c>
@@ -14320,7 +14612,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
         <v>704</v>
       </c>
@@ -14331,7 +14623,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:7">
       <c r="A70" s="2" t="s">
         <v>704</v>
       </c>
@@ -14342,7 +14634,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:7">
       <c r="A71" s="2" t="s">
         <v>704</v>
       </c>
@@ -14353,7 +14645,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:7">
       <c r="A72" s="2" t="s">
         <v>704</v>
       </c>
@@ -14364,7 +14656,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
         <v>704</v>
       </c>
@@ -14375,7 +14667,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
         <v>704</v>
       </c>
@@ -14386,7 +14678,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
         <v>704</v>
       </c>
@@ -14397,7 +14689,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
         <v>704</v>
       </c>
@@ -14408,7 +14700,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
         <v>704</v>
       </c>
@@ -14419,7 +14711,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:7">
       <c r="A78" s="2" t="s">
         <v>704</v>
       </c>
@@ -14430,7 +14722,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
         <v>704</v>
       </c>
@@ -14441,7 +14733,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:7">
       <c r="A80" s="2" t="s">
         <v>704</v>
       </c>

--- a/notes/coreMeasurement/coresScanned_Ai-Lun.xlsx
+++ b/notes/coreMeasurement/coresScanned_Ai-Lun.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temporal Ecology Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB32088-0F8A-40AD-A851-3AEC9FC47CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C292519-3F5C-4077-963D-3DF33AD12CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="1257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3891" uniqueCount="1259">
   <si>
     <t>Stand</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4037,12 +4037,6 @@
     <t>Ai-Lun</t>
   </si>
   <si>
-    <t>Not in folder?</t>
-  </si>
-  <si>
-    <t>Notes - DPI 6472</t>
-  </si>
-  <si>
     <t>dark band of circles near rings 19, 28</t>
   </si>
   <si>
@@ -4061,17 +4055,29 @@
     <t>ring of circles near 70</t>
   </si>
   <si>
-    <t>ring 5 a bit faint but still visible</t>
-  </si>
-  <si>
     <t>gap before 62, might affect ring placement</t>
+  </si>
+  <si>
+    <t>rings 86 and 89 are very thick</t>
+  </si>
+  <si>
+    <t>check ring 83, centre of core also appears</t>
+  </si>
+  <si>
+    <t>check ring 65</t>
+  </si>
+  <si>
+    <t>brown bands between rings 60, 61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4095,6 +4101,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -4127,7 +4140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4145,6 +4158,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13373,7 +13389,9 @@
   <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="3" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="13.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="2"/>
     <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
@@ -13400,7 +13418,7 @@
         <v>1244</v>
       </c>
       <c r="G1" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -13464,7 +13482,7 @@
         <v>103</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -13518,9 +13536,7 @@
         <v>232</v>
       </c>
       <c r="E7"/>
-      <c r="G7" s="7" t="s">
-        <v>1247</v>
-      </c>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
@@ -13636,9 +13652,7 @@
         <v>232</v>
       </c>
       <c r="E13"/>
-      <c r="G13" s="7" t="s">
-        <v>1247</v>
-      </c>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
@@ -13732,9 +13746,7 @@
         <v>232</v>
       </c>
       <c r="E18"/>
-      <c r="G18" s="7" t="s">
-        <v>1247</v>
-      </c>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
@@ -13756,7 +13768,7 @@
         <v>174</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13779,7 +13791,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13880,7 +13892,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -13899,7 +13911,7 @@
         <v>68</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -13983,7 +13995,7 @@
         <v>143</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -14123,7 +14135,7 @@
         <v>144</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -14188,7 +14200,7 @@
         <v>164</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -14597,9 +14609,7 @@
       <c r="F67">
         <v>129</v>
       </c>
-      <c r="G67" s="8" t="s">
-        <v>1255</v>
-      </c>
+      <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
@@ -14611,6 +14621,15 @@
       <c r="C68" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D68" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E68" s="5">
+        <v>46183</v>
+      </c>
+      <c r="F68">
+        <v>129</v>
+      </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
@@ -14622,6 +14641,15 @@
       <c r="C69" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D69" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E69" s="5">
+        <v>46183</v>
+      </c>
+      <c r="F69">
+        <v>129</v>
+      </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2" t="s">
@@ -14633,6 +14661,15 @@
       <c r="C70" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D70" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E70" s="5">
+        <v>46183</v>
+      </c>
+      <c r="F70">
+        <v>111</v>
+      </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2" t="s">
@@ -14644,6 +14681,15 @@
       <c r="C71" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D71" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E71" s="5">
+        <v>46183</v>
+      </c>
+      <c r="F71">
+        <v>85</v>
+      </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2" t="s">
@@ -14655,6 +14701,15 @@
       <c r="C72" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D72" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E72" s="5">
+        <v>46183</v>
+      </c>
+      <c r="F72">
+        <v>113</v>
+      </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
@@ -14666,6 +14721,15 @@
       <c r="C73" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D73" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E73" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F73">
+        <v>111</v>
+      </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
@@ -14677,6 +14741,15 @@
       <c r="C74" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="D74" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E74" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F74">
+        <v>92</v>
+      </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
@@ -14688,6 +14761,15 @@
       <c r="C75" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D75" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E75" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F75">
+        <v>72</v>
+      </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
@@ -14699,6 +14781,15 @@
       <c r="C76" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D76" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E76" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F76">
+        <v>68</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
@@ -14710,9 +14801,18 @@
       <c r="C77" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D77" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E77" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F77">
+        <v>119</v>
+      </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -14720,6 +14820,18 @@
       </c>
       <c r="C78" s="2" t="s">
         <v>361</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E78" s="5">
+        <v>46187</v>
+      </c>
+      <c r="F78">
+        <v>103</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -14732,6 +14844,9 @@
       <c r="C79" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="F79">
+        <v>150</v>
+      </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2" t="s">
@@ -14743,9 +14858,12 @@
       <c r="C80" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="F80">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -14754,8 +14872,20 @@
       <c r="C81" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E81" s="5">
+        <v>46192</v>
+      </c>
+      <c r="F81">
+        <v>121</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="2" t="s">
         <v>704</v>
       </c>
@@ -14765,8 +14895,17 @@
       <c r="C82" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E82" s="5">
+        <v>46192</v>
+      </c>
+      <c r="F82">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
         <v>704</v>
       </c>
@@ -14776,8 +14915,17 @@
       <c r="C83" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E83" s="5">
+        <v>46192</v>
+      </c>
+      <c r="F83">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="2" t="s">
         <v>704</v>
       </c>
@@ -14787,9 +14935,18 @@
       <c r="C84" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="D84" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E84" s="5">
+        <v>46192</v>
+      </c>
+      <c r="F84">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -14798,8 +14955,20 @@
       <c r="C85" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E85" s="5">
+        <v>46192</v>
+      </c>
+      <c r="F85">
+        <v>67</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="2" t="s">
         <v>704</v>
       </c>
@@ -14809,8 +14978,17 @@
       <c r="C86" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E86" s="5">
+        <v>46203</v>
+      </c>
+      <c r="F86">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="2" t="s">
         <v>704</v>
       </c>
@@ -14820,8 +14998,17 @@
       <c r="C87" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E87" s="5">
+        <v>46203</v>
+      </c>
+      <c r="F87">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
         <v>704</v>
       </c>
@@ -14831,8 +15018,17 @@
       <c r="C88" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E88" s="5">
+        <v>46203</v>
+      </c>
+      <c r="F88">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="2" t="s">
         <v>704</v>
       </c>
@@ -14842,8 +15038,17 @@
       <c r="C89" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E89" s="5">
+        <v>46203</v>
+      </c>
+      <c r="F89">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" s="2" t="s">
         <v>704</v>
       </c>
@@ -14853,8 +15058,17 @@
       <c r="C90" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E90" s="5">
+        <v>46203</v>
+      </c>
+      <c r="F90">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" s="2" t="s">
         <v>704</v>
       </c>
@@ -14864,8 +15078,17 @@
       <c r="C91" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="D91" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E91" s="5">
+        <v>46205</v>
+      </c>
+      <c r="F91">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="2" t="s">
         <v>704</v>
       </c>
@@ -14875,8 +15098,17 @@
       <c r="C92" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="D92" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E92" s="5">
+        <v>46205</v>
+      </c>
+      <c r="F92">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="2" t="s">
         <v>704</v>
       </c>
@@ -14886,8 +15118,17 @@
       <c r="C93" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="D93" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E93" s="5">
+        <v>46205</v>
+      </c>
+      <c r="F93">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="2" t="s">
         <v>704</v>
       </c>
@@ -14897,8 +15138,17 @@
       <c r="C94" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="D94" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E94" s="5">
+        <v>46205</v>
+      </c>
+      <c r="F94">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
         <v>704</v>
       </c>
@@ -14908,8 +15158,17 @@
       <c r="C95" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="D95" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E95" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F95">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="2" t="s">
         <v>704</v>
       </c>
@@ -14918,6 +15177,15 @@
       </c>
       <c r="C96" s="2" t="s">
         <v>361</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E96" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F96">
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -14930,6 +15198,15 @@
       <c r="C97" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D97" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E97" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F97">
+        <v>63</v>
+      </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
@@ -14941,6 +15218,15 @@
       <c r="C98" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D98" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E98" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F98">
+        <v>54</v>
+      </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2" t="s">
@@ -14952,6 +15238,15 @@
       <c r="C99" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D99" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E99" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F99">
+        <v>95</v>
+      </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2" t="s">
@@ -14963,6 +15258,15 @@
       <c r="C100" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D100" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E100" s="5">
+        <v>46213</v>
+      </c>
+      <c r="F100">
+        <v>120</v>
+      </c>
       <c r="G100" s="2" t="s">
         <v>1242</v>
       </c>
@@ -14977,6 +15281,15 @@
       <c r="C101" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D101" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E101" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F101">
+        <v>112</v>
+      </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
@@ -14988,6 +15301,15 @@
       <c r="C102" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D102" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E102" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F102">
+        <v>116</v>
+      </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2" t="s">
@@ -14999,9 +15321,18 @@
       <c r="C103" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D103" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E103" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F103">
+        <v>67</v>
+      </c>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -15009,6 +15340,18 @@
       </c>
       <c r="C104" s="2" t="s">
         <v>361</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E104" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F104">
+        <v>69</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>1257</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -15021,6 +15364,15 @@
       <c r="C105" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D105" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E105" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F105">
+        <v>97</v>
+      </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
@@ -15043,6 +15395,15 @@
       <c r="C107" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D107" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E107" s="5">
+        <v>46214</v>
+      </c>
+      <c r="F107">
+        <v>129</v>
+      </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2" t="s">
@@ -15054,6 +15415,15 @@
       <c r="C108" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D108" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E108" s="5">
+        <v>46217</v>
+      </c>
+      <c r="F108">
+        <v>115</v>
+      </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2" t="s">
@@ -15065,6 +15435,15 @@
       <c r="C109" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D109" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E109" s="5">
+        <v>46217</v>
+      </c>
+      <c r="F109">
+        <v>124</v>
+      </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
@@ -15076,6 +15455,15 @@
       <c r="C110" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D110" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E110" s="5">
+        <v>46217</v>
+      </c>
+      <c r="F110">
+        <v>110</v>
+      </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
@@ -15087,6 +15475,15 @@
       <c r="C111" s="2" t="s">
         <v>361</v>
       </c>
+      <c r="D111" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E111" s="5">
+        <v>46217</v>
+      </c>
+      <c r="F111">
+        <v>123</v>
+      </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
@@ -15098,8 +15495,17 @@
       <c r="C112" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="D112" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E112" s="5">
+        <v>46217</v>
+      </c>
+      <c r="F112">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>704</v>
       </c>
@@ -15109,8 +15515,17 @@
       <c r="C113" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="D113" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E113" s="5">
+        <v>46223</v>
+      </c>
+      <c r="F113">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>704</v>
       </c>
@@ -15120,8 +15535,17 @@
       <c r="C114" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="D114" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E114" s="5">
+        <v>46223</v>
+      </c>
+      <c r="F114">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>704</v>
       </c>
@@ -15131,8 +15555,17 @@
       <c r="C115" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="D115" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E115" s="5">
+        <v>46223</v>
+      </c>
+      <c r="F115">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>704</v>
       </c>
@@ -15142,8 +15575,17 @@
       <c r="C116" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="D116" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E116" s="5">
+        <v>46223</v>
+      </c>
+      <c r="F116">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>704</v>
       </c>
@@ -15153,8 +15595,17 @@
       <c r="C117" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="D117" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E117" s="5">
+        <v>46223</v>
+      </c>
+      <c r="F117">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>704</v>
       </c>
@@ -15165,7 +15616,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>704</v>
       </c>
@@ -15176,7 +15627,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>704</v>
       </c>
@@ -15187,7 +15638,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>704</v>
       </c>
